--- a/www/download/COUNTRY.CYP.WIOD13.xlsx
+++ b/www/download/COUNTRY.CYP.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Chipre</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.772678123777948</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.796685775755041</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.877292976582033</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.883384436593682</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.926586570603177</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.06079414511591</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.09817702407959</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.03987932720202</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.882706029234349</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.799673759926997</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.792091754634952</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.783471856320399</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.727151112510703</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.679902076410497</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948682306625</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.314880975756053</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.289474802170022</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.471816514580483</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.384281673770632</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.247021010466021</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.297179398557758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>0.224951428731801</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>0.208508449438505</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.0960695945635355</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.0840927889528962</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.104189979386306</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.127523764830177</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>0.272229515988968</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>0.113596063371232</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.355662415923796</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>1.12912026704838</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>1.0750064179935</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>1.37082719674942</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>1.27400667923295</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>1.06963846717267</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>1.17742259222568</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0.966595783094154</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>0.940005540921056</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>0.77286973327843</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.811209425453014</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.838961691808536</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.925905320250997</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>1.16685272736336</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.898464122391809</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>1.32383170165371</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>556.844</t>
+          <t>1.72354989834663</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>559.558</t>
+          <t>1.64593804664611</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>565.864</t>
+          <t>2.03737408385412</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>576.508</t>
+          <t>1.90868321718894</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>590.902</t>
+          <t>1.61646009087486</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>605.96</t>
+          <t>1.8024226058179</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>626.986</t>
+          <t>1.58566527430868</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>631.03</t>
+          <t>1.54386100099298</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>652.422</t>
+          <t>1.04741079377908</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>663.882</t>
+          <t>1.45433807708323</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>679.879</t>
+          <t>1.53832735913445</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>694.745</t>
+          <t>1.59780893732621</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>715.064</t>
+          <t>1.93527959465579</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>724.744</t>
+          <t>1.47818030458251</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>725.571</t>
+          <t>2.07021356319294</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>385.082</t>
+          <t>602724856.904596</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>388.735</t>
+          <t>658777890.430236</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>393.173</t>
+          <t>583928303.278531</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>400.651</t>
+          <t>590188040.243696</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>410.296</t>
+          <t>657974051.818377</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>421.155</t>
+          <t>633032530.321017</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>433.872</t>
+          <t>699161442.195938</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>443.031</t>
+          <t>720663275.749064</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>455.955</t>
+          <t>747992730.910851</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>458.638</t>
+          <t>710974631.680326</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>473.113</t>
+          <t>647356359.309991</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>494.479</t>
+          <t>664964217.514133</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>516.413</t>
+          <t>642171810.008181</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>540.57</t>
+          <t>890342089.993768</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>541.705</t>
+          <t>588458183.065813</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>205502165.442021</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>213630679.915114</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>186947225.143701</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>197479290.059014</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>224960211.180862</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>220536803.809869</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>247046723.383002</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>257524220.903282</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>298639466.166068</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>289621412.642241</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>291553210.598619</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>299270826.295426</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>281642240.262292</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>342221459.922936</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>279717315.800882</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>2014593.62749617</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>2073405.15530827</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>2027558.64583715</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>2003178.0119987</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>2326219.28211236</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>2280179.27437245</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>2333241.01541893</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>2136637.20843423</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>1855338.57911541</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>1619600.01178018</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>1325511.54551017</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>1241253.66223678</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>1021245.85170978</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>1192558.10858618</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>829113.640695164</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>2050.96203839294</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>2038.08169754216</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>2011.75227907708</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.19</t>
+          <t>1997.86414175909</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>2045.52610243457</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>2133.14894099297</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>2089.44688339496</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>2135.20238996816</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>2379.49268825162</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>2666.10781394578</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>2870.10480024534</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>3043.26953238187</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>3503.69015405283</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>3813.11196518307</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>3600.70193396355</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>4692.37759154638</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>5166.89700537609</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>4550.42831800548</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>4573.97989983913</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>5210.05213847406</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>5215.40836282184</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>5609.28864053445</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>5910.79029674408</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>6608.28794648945</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>6922.25532823096</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>6750.32823477782</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>7267.19004576828</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>7939.57043878493</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>12186.9312881208</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>7513.37510620318</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>0.873857773524042</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>0.819660071006088</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>1.10312329070225</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>1.02882384867275</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>0.823858758799705</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>0.90968125376066</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>0.756234586148946</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>0.720346919004516</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>0.526774092699628</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>0.583577663736276</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>0.622732944797972</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.652279328797231</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>0.833577944555002</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>42.58</t>
+          <t>0.579591180873721</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>42.93</t>
+          <t>0.93661589540497</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>1799.88851864952</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>1884.67848454279</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>1840.40126977649</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>1997.08119499064</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>2291.93478452602</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>1884.68778117339</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>1902.94007258066</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>2216.68999777257</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>2575.6201023762</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>2940.90539275184</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>2990.47972834511</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>3335.66862591975</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>3861.97986126612</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>4675.69892152338</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.772678123777948</t>
+          <t>918.582982574662</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.796685775755041</t>
+          <t>945.531448094609</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.877292976582033</t>
+          <t>817.208769110758</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.883384436593682</t>
+          <t>846.509637541854</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.926586570603177</t>
+          <t>945.278283489495</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.06079414511591</t>
+          <t>912.440230905542</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.09817702407959</t>
+          <t>995.35343828768</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.03987932720202</t>
+          <t>1007.52825079531</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.882706029234349</t>
+          <t>1135.94319576291</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.799673759926997</t>
+          <t>1057.39836671136</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.792091754634952</t>
+          <t>1020.13019803576</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.783471856320399</t>
+          <t>1010.70863321657</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.727151112510703</t>
+          <t>912.053886859755</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902076410497</t>
+          <t>1047.83055702063</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948682306625</t>
+          <t>859.610681625329</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>17729245.1362546</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>31715876.4692147</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2152492.84044062</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>24205121.9236704</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>94917690.9947271</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>87501719.5564436</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>135637136.02422</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>87400502.2824607</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>104682249.161742</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>95342161.5306249</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>84235200.3277923</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>85576648.8789831</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>19189668.9953318</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>176766507.072575</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>84643046.5097518</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>19537945.6012788</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>41607770.6735433</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>14924546.7277712</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>29041394.8467529</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>95706341.4995635</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>97541926.8986814</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>139812156.836123</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>85199485.4395673</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>115729028.163408</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>68107878.7212638</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14243217.4738318</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>42296151.8348083</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-10023562.3329527</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>140487629.552005</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>33729526.0714515</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-1808700.46502428</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-9891894.20432859</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>-12772053.8873306</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-4836272.92308251</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>-788650.504836419</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-10040207.3422377</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-4175020.81190273</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2201016.84289349</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>-11046779.0016654</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>27234282.8093611</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>69991982.8539605</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>43280497.0441747</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>29213231.3282846</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>36278877.5205704</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50913520.4383002</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1721.29386252443</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1720.54582197833</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1718.69079568295</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1717.41894077624</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1724.05407684547</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1742.47000413736</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1748.07413376309</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1733.29812206573</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1734.32864206923</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1674.47243519533</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1655.3988803359</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1669.97298210064</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1672.32189119171</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1655.14390691978</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1664.73570989551</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1880.59439378588</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1879.60362781323</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1889.36227045075</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1895.78428148635</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1907.36604260813</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1924.90470139771</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1947.76638707673</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1922.11392019494</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1914.3838028169</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1879.08859326352</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1855.56495633188</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1865.5880773362</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1859.72431729519</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1852.77628972653</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1848.05901025774</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>1986.75605591144</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>2113.1513598131</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>2064.14002772178</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>2082.82920060218</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>26.99</t>
+          <t>2162.24533912994</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>2147.15485544231</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>2290.77504501028</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>2299.08485759001</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>2752.51981074515</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>3347.5841392997</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>3450.0903690429</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>3796.76966358804</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>4611.57890213568</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>5147.43092485272</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>4628.49509079995</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>112.89</t>
+          <t>148574468.180658</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>164916994.531615</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>137.07</t>
+          <t>144915307.267119</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>127.4</t>
+          <t>143156751.067901</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>110.77</t>
+          <t>159993440.816746</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>117.72</t>
+          <t>161246757.663278</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>96.63</t>
+          <t>181580667.462153</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>93.97</t>
+          <t>175654859.916623</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>182418370.268062</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>81.12</t>
+          <t>154776730.190298</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>108171009.055264</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>129991916.161978</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>116.66</t>
+          <t>143261593.878699</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>89.85</t>
+          <t>169440535.432707</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>132.37</t>
+          <t>105329391.092983</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>172.32</t>
+          <t>3903.81993369891</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>164.57</t>
+          <t>4188.43247851129</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>203.72</t>
+          <t>4019.55139186513</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>4033.88415550994</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>166.45</t>
+          <t>4092.21245558792</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>180.22</t>
+          <t>4242.13096642063</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>158.53</t>
+          <t>4402.20095822659</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>154.35</t>
+          <t>4735.10396469906</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>104.72</t>
+          <t>5495.71255800651</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>145.44</t>
+          <t>6384.3116209553</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>153.83</t>
+          <t>6664.35606501167</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>159.77</t>
+          <t>7593.47009763796</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>9632.78411611902</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>147.82</t>
+          <t>11415.8392821631</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>207.01</t>
+          <t>8671.10649166191</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>556.844</t>
+          <t>462295108.392554</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>559.558</t>
+          <t>504221735.377034</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>565.864</t>
+          <t>414649708.75541</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>576.508</t>
+          <t>448425908.44106</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>590.902</t>
+          <t>545160087.895888</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>605.96</t>
+          <t>559743545.996008</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>626.986</t>
+          <t>646764234.119646</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>631.03</t>
+          <t>638996376.549051</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>652.422</t>
+          <t>686555067.964336</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>663.882</t>
+          <t>655644596.720543</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>679.879</t>
+          <t>590256867.035607</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>694.745</t>
+          <t>644233869.509778</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>715.064</t>
+          <t>662230579.232104</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>724.744</t>
+          <t>898470485.764876</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>725.571</t>
+          <t>581621927.76868</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>385.082</t>
+          <t>-1917.06387778747</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>388.735</t>
+          <t>-2075.28111869819</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>393.173</t>
+          <t>-1955.41136414335</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>400.651</t>
+          <t>-1951.05495490776</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>410.296</t>
+          <t>-1929.96711645797</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>421.155</t>
+          <t>-2094.97611097832</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>433.872</t>
+          <t>-2111.42591321631</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>443.031</t>
+          <t>-2436.01910710905</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>455.955</t>
+          <t>-2743.19274726135</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>458.638</t>
+          <t>-3036.7274816556</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>473.113</t>
+          <t>-3214.26569596877</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>494.479</t>
+          <t>-3796.70043404992</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>516.413</t>
+          <t>-5021.20521398334</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>540.57</t>
+          <t>-6268.4083573104</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>541.705</t>
+          <t>-4042.61140086197</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>602.809</t>
+          <t>-313720640.211896</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>658.847</t>
+          <t>-339304740.845419</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>583.979</t>
+          <t>-269734401.488291</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>590.181</t>
+          <t>-305269157.373158</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>644.239</t>
+          <t>-385166647.079141</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>633.095</t>
+          <t>-398496788.33273</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>699.294</t>
+          <t>-465183566.657494</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>720.78</t>
+          <t>-463341516.632427</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>748.043</t>
+          <t>-504136697.696274</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>710.978</t>
+          <t>-500867866.530244</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>647.379</t>
+          <t>-482085857.980344</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>665.008</t>
+          <t>-514241953.3478</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>642.247</t>
+          <t>-518968985.353405</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>890.354</t>
+          <t>-729029950.33217</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>588.486</t>
+          <t>-476292536.675697</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3289.33855</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3301.17601</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3070.01195</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3277.96135</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3227.9768</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2970.60471</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>3048.41562</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>3366.44822</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4252.8315</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4995.28712</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>5266.43538</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>5524.38471</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6331.55874</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>7278.69535</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6796.58128</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>263.441</t>
+          <t>0.0375658060427179</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>259.855</t>
+          <t>0.034166543971893</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>258.156</t>
+          <t>0.0321017832575377</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>257.788</t>
+          <t>0.0388482548338946</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>258.328</t>
+          <t>0.0343853455290794</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>258.916</t>
+          <t>0.0443745865568103</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>260.436</t>
+          <t>0.0461503177158751</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>260.331</t>
+          <t>0.0353058108325397</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>269.335</t>
+          <t>0.0324699128641394</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>273.832</t>
+          <t>0.0354964163417114</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>275.243</t>
+          <t>0.0367006149202225</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>278.466</t>
+          <t>0.0362360676525943</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>283.387</t>
+          <t>0.0420027763244121</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>278.575</t>
+          <t>0.0387955883339712</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>282.012</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4009.30204461226</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4110.62893189141</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3985.18004554325</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4160.21885548685</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4226.76494684178</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3977.86902232336</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4095.1821265542</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4664.52482765077</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>6094.95444184257</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>7135.12399070072</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>7639.76272830467</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>8245.92046224411</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>9545.39955151358</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>11024.2451353322</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>10604.365021569</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>205.528</t>
+          <t>5284.91893755531</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>213.651</t>
+          <t>5428.85074392709</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>186.961</t>
+          <t>5270.72917188927</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>197.477</t>
+          <t>5483.52170324111</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>220.902</t>
+          <t>5598.45614178127</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>220.557</t>
+          <t>5290.57706587232</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>247.081</t>
+          <t>5477.72397844922</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>257.565</t>
+          <t>6144.2804408705</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>298.665</t>
+          <t>8016.30446858495</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>289.618</t>
+          <t>9440.96012703077</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>291.56</t>
+          <t>10170.0773856905</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>299.284</t>
+          <t>10905.9669471042</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>281.671</t>
+          <t>12486.3005746237</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>342.224</t>
+          <t>14467.4037383969</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>279.728</t>
+          <t>13817.1416338568</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>36529.8037857805</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>81.95</t>
+          <t>37487.7032509869</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>110.3</t>
+          <t>35563.213394576</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>36751.9667967827</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>36265.9523848064</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>32633.2348156165</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>33016.6545840697</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>72.01</t>
+          <t>36533.9452894855</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>52.66</t>
+          <t>45002.8512596556</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>58.36</t>
+          <t>53359.7893934907</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>62.27</t>
+          <t>57946.9071727335</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>62627.0932247143</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>72474.0691091171</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>86099.5392394877</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>93.65</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.015</t>
+          <t>5284.91893755531</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.074</t>
+          <t>5455.39135868644</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.028</t>
+          <t>5645.12988085847</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.003</t>
+          <t>5745.15417948743</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.254</t>
+          <t>6005.84982413465</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>6349.97905401159</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>6647.25188224167</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.137</t>
+          <t>7098.23950453184</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>7575.489937585</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>8045.80011186733</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>8497.11821011226</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.241</t>
+          <t>8705.03496547207</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>8949.51823133714</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>9176.45124006597</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>9087.11431011384</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4009.30204461226</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4126.86311251552</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4270.32832980622</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4369.6860878491</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4512.5640103078</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4742.11401089715</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4921.84600579111</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5363.73180868011</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5738.08342482409</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6066.29332678926</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>6391.84905601753</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>6596.88058665277</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6858.45153611619</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7047.65434601301</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>7008.56538602621</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3172.16004244469</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3165.50374607291</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2982.04383811073</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3424.83096675889</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3538.95208821873</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3332.77408412768</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3426.66917155078</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3506.5505591295</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4036.85876141505</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4834.98669296923</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5117.16685430948</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5605.02821289582</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>6906.09197537635</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>8015.98120160314</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>7436.5410161432</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>385081830.189556</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>388735218.183415</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>393173063.331875</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>400650693.290692</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>410295651.543646</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>421155000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>433872000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>443031000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>455955000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>458638000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>473113000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>494479000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>516413000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>540570000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>541705000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>556844000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>559558000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>565864000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>576508000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>590902000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>605960000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>626986000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>631030000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>652422000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>663882000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>679879000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>694745000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>715064000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>724744333.122296</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>725571484.03977</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>263441246.359666</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>259854833.536317</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>258155719.163838</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>257787648.463305</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>258328143.739714</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>258916000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>260436000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>260331000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>269335000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>273832000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>275243000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>278466000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>283387000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>278574974.798666</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>282012076.845781</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>296100</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>297700</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>299500</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>304100</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>309800</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>314800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>321900</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>328300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>340800</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>353300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>366400</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>372400</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>384500</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>391166.670871672</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>392612.725033373</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>223716.495232719</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>225937.149256762</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>228763.11685584</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>233286.523036485</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>237983.052303308</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>241700</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>248200</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>255600</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>262900</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>273900</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>285800</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>296100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>308800</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>326600</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>325400</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>556844000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>559558000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>565864000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>576508000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>590902000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>605960000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>626986000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>631030000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>652422000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>663882000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>679879000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>694745000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>715064000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>724744333.122296</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>725571484.03977</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>385081830.189556</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>388735218.183415</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>393173063.331875</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>400650693.290692</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>410295651.543646</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>421155000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>433872000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>443031000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>455955000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>458638000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>473113000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>494479000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>516413000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>540570000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>541705000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.390116927880701</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.384904366830866</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.369970763777891</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.352881576519591</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.353397642917275</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.358280413431593</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.353910440875485</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.358248084348114</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.339631106733564</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.364859725162261</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.347331262498627</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.353356172580841</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.36971202850082</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.361581828929178</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.361957673459242</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.321293200762932</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.328626938735117</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.322348896331952</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.315242186789605</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.337233876652075</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.342979664793355</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.349594082475155</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.348925892107897</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.338509157324964</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.365575717545096</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.379463226115965</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.387763044649832</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.383128728066806</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.395468700852395</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.399773244605587</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.288589871356368</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.286468694434018</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.307680339890158</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.331876236690805</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.30936848043065</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.298739921775052</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.296495476649359</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.292826023543989</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.321859735941472</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.269564557292643</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.273205511385408</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.258880782769327</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.247159243432374</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.242949470218427</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.238269081935171</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.29501632942481</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.293308740062344</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.280608690472955</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.267314716451038</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.267813512574648</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.271519071909591</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.271893085468395</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.278524698977206</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.280286225135778</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.279550377287939</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.265568736297898</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.274163910756846</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.293637463282541</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.302300726860568</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.302163821283627</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.359447173559755</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.367002576026058</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.358082664819624</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.347848501886329</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.371520788571168</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.377445256022587</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.382594963330836</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.380685901781172</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.390437025126417</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.403575019887614</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.416900756395004</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.428554835823112</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.420868018826323</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.425813446969654</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.429346185139048</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.345536497015435</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.339688683911597</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.361308644707421</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.384836781662633</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.360665698854184</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.351035672067821</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.345511951200769</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.340789399241622</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.329276749737806</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.316874602824447</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.317530507307097</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.297281253420042</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.285494517891135</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.271885826169778</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.268489993577326</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>13745.56817</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>14025.103</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>13541.08615</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>14456.44642</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>14904.16569</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>14176.64369</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>14825.93409</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>16295.25573</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>20252.26861</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>23628.63618</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>25577.21377</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>28109.62515</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>33700.83554</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>40127.54318</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>37463.21071</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>8457.07898</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8594.35449</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8252.77301</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8908.35267</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>9137.40823</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>8623.35115</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8904.39315</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9650.831</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>12053.16323</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>14275.94682</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>15287.24424</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>16510.99516</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>19392.39255</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>22483.38494</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>21253.68265</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>28225.7804786168</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>28703.0313879198</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>29087.669044844</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>29535.6804326495</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>29943.9567213731</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>30381.0747399953</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30840.3990575789</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>31403.4282774735</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>31951.0194714376</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>32656.6168437408</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>33395.9865417147</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>34307.1617116782</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>35470.9755419079</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>36716.5888590675</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
